--- a/docs/test-cases/SPM-22_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-22_Test_Cases.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -69,6 +69,9 @@
     <font>
       <name val="Arial"/>
       <color theme="1"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -154,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -221,6 +224,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -513,12 +519,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="25">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>SPM-22: As a ConnectSphere user, I want the interface to show me only the navigation, screens and actions appropriate to my role so that I can't see or reach functionality I'm not authorised for</t>
         </is>
@@ -530,32 +536,32 @@
     </row>
     <row r="2" ht="12.75" customHeight="1" s="25"/>
     <row r="3" ht="12.75" customHeight="1" s="25">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -582,27 +588,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC01</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>An Attendee's sidebar offers only the Attendee screens</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -621,27 +627,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC02</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>An Event Coordinator's sidebar offers the coordinator's working screens</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -660,27 +666,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC03</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Venue Staff and Technical Support get different sidebars from each other</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -699,27 +705,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC04</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>An Attendee opening an event sees only the Overview tab</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -738,27 +744,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC05</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>An Event Coordinator opening an event sees the Overview and Equipment tabs</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -777,27 +783,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC06</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Venue Staff opening an event sees only the tabs that exist for them</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -816,27 +822,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC07</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>A Coordinator sees no Add venue control on the venue catalogue</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -855,27 +861,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC08</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Venue Staff do get the Add venue control on the same screen</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -894,27 +900,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC09</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Refusals are never expressed as a disabled control</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -933,27 +939,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC10</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>The New event request action appears only for an Organiser</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -972,27 +978,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC11</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>An Attendee typing the Venues address is refused and sees no venue data</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1011,38 +1017,42 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC12</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>An Operations Manager typing the Review Queue address is refused</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="12.75" customHeight="1" s="25">
       <c r="A16" s="16" t="inlineStr">
@@ -1050,27 +1060,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC13</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>A Coordinator typing the New event request address is refused at the door</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1089,38 +1099,42 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC14</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>An Attendee typing the Assignments address is refused</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="25">
       <c r="A18" s="16" t="inlineStr">
@@ -1128,27 +1142,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC15</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>A signed-out visitor typing a restricted address is sent to log in</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1167,38 +1181,42 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC16</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>A permitted role opening a screen that is not built yet is told so, not shown a 404</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>AC4, AC6</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H19" s="29" t="n"/>
-      <c r="I19" s="29" t="n"/>
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="12.75" customHeight="1" s="25">
       <c r="A20" s="16" t="inlineStr">
@@ -1206,27 +1224,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC17</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Internal planning fields are absent from an Attendee's view of an event</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1245,27 +1263,27 @@
           <t>TC18</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC18</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>The same event shows its internal fields to a Coordinator</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1284,38 +1302,42 @@
           <t>TC19</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC19</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>The Operations Manager's navigation matches their permissions</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H22" s="29" t="n"/>
-      <c r="I22" s="29" t="n"/>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="12.75" customHeight="1" s="25">
       <c r="A23" s="16" t="inlineStr">
@@ -1323,55 +1345,59 @@
           <t>TC20</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC20</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Every item in the Operations Manager's sidebar opens without an error</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H23" s="29" t="n"/>
-      <c r="I23" s="29" t="n"/>
+      <c r="I23" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="12.75" customHeight="1" s="25"/>
     <row r="25" ht="12.75" customHeight="1" s="25"/>
     <row r="26" ht="12.75" customHeight="1" s="25">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C26" s="26" t="n"/>
       <c r="D26" s="27" t="n"/>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1379,19 +1405,19 @@
       <c r="F26" s="27" t="n"/>
     </row>
     <row r="27" ht="44.25" customHeight="1" s="25">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>Given my role, when I view the main navigation, then only the nav items defined for my role are shown (e.g. an Attendee sees Browse Events and My Registrations, not Review Queue, Venues, or Assignments).</t>
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="27" t="n"/>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC01
 SPM-22-TC02
@@ -1401,19 +1427,19 @@
       <c r="F27" s="27" t="n"/>
     </row>
     <row r="28" ht="44.25" customHeight="1" s="25">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>Given my role, when I open an event's detail page, then only the tabs permitted for my role are rendered (e.g. an Attendee sees only Overview; Venue Staff sees only Overview and Venue).</t>
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="27" t="n"/>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC04
 SPM-22-TC05
@@ -1423,19 +1449,19 @@
       <c r="F28" s="27" t="n"/>
     </row>
     <row r="29" ht="57.75" customHeight="1" s="25">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Given an action is not permitted for my role, when the relevant screen renders, then the corresponding button, link or tab is not shown at all, rather than shown disabled.</t>
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="27" t="n"/>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC07
 SPM-22-TC08
@@ -1446,19 +1472,19 @@
       <c r="F29" s="27" t="n"/>
     </row>
     <row r="30" ht="84.75" customHeight="1" s="25">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>Given I navigate directly to a URL for a screen outside my role's permissions, when the page loads, then I see an access-denied state or am redirected, and no restricted data is rendered.</t>
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="27" t="n"/>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC11
 SPM-22-TC12
@@ -1471,19 +1497,19 @@
       <c r="F30" s="27" t="n"/>
     </row>
     <row r="31" ht="57.75" customHeight="1" s="25">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Given fields are restricted to internal roles (e.g. coordinator assignment, rejection reasons, venue/equipment arrangements), when an Attendee views an event, then those fields are absent from the page, not merely blank.</t>
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="27" t="n"/>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC17
 SPM-22-TC18</t>
@@ -1492,19 +1518,19 @@
       <c r="F31" s="27" t="n"/>
     </row>
     <row r="32" ht="44.25" customHeight="1" s="25">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>Given the Operations Manager role, when they use the interface, then they see the Assignments and All Events navigation matching their permissions.</t>
         </is>
       </c>
       <c r="C32" s="26" t="n"/>
       <c r="D32" s="27" t="n"/>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC16
 SPM-22-TC19
@@ -1515,12 +1541,12 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" s="25"/>
     <row r="34" ht="192.75" customHeight="1" s="25">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>src/lib/roles.ts
 src/lib/permissions.ts
@@ -2583,7 +2609,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC08</t>
         </is>
@@ -2595,7 +2621,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff, who hold venue management.</t>
         </is>
@@ -2607,7 +2633,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open Venues from the sidebar
 2. Wait for the venue list to finish loading
@@ -2621,7 +2647,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: marcus.wong@connectsphere.com (Venue Staff)</t>
         </is>
@@ -2633,7 +2659,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>An Add venue button is shown and is fully enabled, and clicking it opens the Add venue form.
 This is the same screen as SPM-22-TC07, proving the control is added for the permitted role rather than hidden for everyone.</t>
@@ -2646,7 +2672,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -2678,7 +2704,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>On the same screen as Venue Staff, exactly one Add venue button was present and fully enabled; clicking it opened the Add venue form.</t>
         </is>
@@ -2702,7 +2728,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Read together with SPM-22-TC07 this shows the control is added for the permitted role rather than hidden from everyone.</t>
         </is>
@@ -2714,7 +2740,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -2745,7 +2771,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>An Add venue button is shown and is fully enabled, and clicking it opens the Add venue form.
 This is the same screen as SPM-22-TC07, proving the control is added for the permitted role rather than hidden for everyone.</t>
@@ -2770,7 +2796,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2782,7 +2808,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3810,7 +3836,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC09</t>
         </is>
@@ -3822,7 +3848,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), an Event Coordinator.</t>
         </is>
@@ -3834,7 +3860,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open Venues from the sidebar and wait for it to load
 2. Try to click every button and link on the page in turn
@@ -3848,7 +3874,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator)</t>
         </is>
@@ -3860,7 +3886,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Every control on the page responds when clicked.
 No control is present-but-greyed-out as a way of saying the coordinator may not use it — controls they may not use are absent instead.</t>
@@ -3873,7 +3899,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -3905,7 +3931,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Every control on the Venues page responded when clicked. A sweep of the page found zero elements carrying disabled or aria-disabled='true'.</t>
         </is>
@@ -3929,7 +3955,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3941,7 +3967,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -3972,7 +3998,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Every control on the page responds when clicked.
 No control is present-but-greyed-out as a way of saying the coordinator may not use it — controls they may not use are absent instead.</t>
@@ -3997,7 +4023,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4009,7 +4035,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5037,7 +5063,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC10</t>
         </is>
@@ -5049,7 +5075,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Demo data is seeded. No one is signed in.</t>
         </is>
@@ -5061,7 +5087,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Log in as rachel.ng@meridianfina.com with password123 and look at the top right of the Dashboard
 2. Log out, then log in as daniel.tan@connectsphere.com with password123
@@ -5075,7 +5101,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Accounts: rachel.ng@meridianfina.com (Event Organiser), daniel.tan@connectsphere.com (Event Coordinator); Password: password123</t>
         </is>
@@ -5087,7 +5113,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Rachel Ng's Dashboard shows a New event request button.
 Daniel Tan's Dashboard shows no such button anywhere — it is absent, not disabled.</t>
@@ -5100,7 +5126,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -5132,7 +5158,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Rachel Ng's Dashboard carried one New event request button. Daniel Tan's Dashboard carried none - the control was absent, not greyed out.</t>
         </is>
@@ -5156,7 +5182,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5168,7 +5194,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN (</t>
         </is>
@@ -5199,7 +5225,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Rachel Ng's Dashboard shows a New event request button.
 Daniel Tan's Dashboard shows no such button anywhere — it is absent, not disabled.</t>
@@ -5224,7 +5250,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5236,7 +5262,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6264,7 +6290,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC11</t>
         </is>
@@ -6276,7 +6302,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Lim (daniel.lim@example.com / password123), an Attendee, whose sidebar does not offer Venues.</t>
         </is>
@@ -6288,7 +6314,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Type the Venues page address directly into the browser address bar and press Enter
 2. Wait for the page to finish loading
@@ -6302,7 +6328,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.lim@example.com (Attendee); Page requested: Venues</t>
         </is>
@@ -6314,7 +6340,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The page shows the heading Venues and a message 'You do not have access to this', explaining that the venue catalogue is for ConnectSphere staff, plus a Back to Dashboard button.
 No venue name, building, capacity or opening hours appears anywhere on the page.</t>
@@ -6327,7 +6353,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -6359,7 +6385,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>The page showed the heading Venues with 'You do not have access to this - The venue catalogue is for ConnectSphere staff.' and a Back to Dashboard button. No venue name, building, capacity or opening hours appeared anywhere on the page.</t>
         </is>
@@ -6383,7 +6409,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>The venue list is never requested: the guard renders in place of the screen, so no venue data reaches the browser at all.</t>
         </is>
@@ -6395,7 +6421,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -6426,7 +6452,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The page shows the heading Venues and a message 'You do not have access to this', explaining that the venue catalogue is for ConnectSphere staff, plus a Back to Dashboard button.
 No venue name, building, capacity or opening hours appears anywhere on the page.</t>
@@ -6451,7 +6477,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6463,7 +6489,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7469,7 +7495,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -7477,70 +7503,77 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-22-TC12</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="44.25" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager. Reviewing requests belongs to the Event Coordinator.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-22-TC12</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44.25" customHeight="1" s="25">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager. Reviewing requests belongs to the Event Coordinator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="25">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Type the Review Queue page address directly into the browser address bar and press Enter
 2. Wait for the page to finish loading</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Account: grace.lim@connectsphere.com (Operations Manager); Page requested: Review Queue</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="84.75" customHeight="1" s="25">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Account: grace.lim@connectsphere.com (Operations Manager); Page requested: Review Queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>The page shows 'You do not have access to this' with the explanation that reviewing event requests is the Event Coordinator's role, and a Back to Dashboard button.
 No list of events awaiting review is shown.
@@ -7548,112 +7581,112 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="71.25" customHeight="1" s="25">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="71.25" customHeight="1" s="25">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>The page showed 'You do not have access to this - Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' with a Back to Dashboard button. No queue of events was shown and no 404 page appeared.</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" s="25">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>The page showed 'You do not have access to this - Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' with a Back to Dashboard button. No queue of events was shown and no 404 page appeared.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" s="25">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="25">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
-    <row r="17" ht="15.75" customHeight="1" s="25">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="B18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>The page shows 'You do not have access to this' with the explanation that reviewing event requests is the Event Coordinator's role, and a Back to Dashboard button.
 No list of events awaiting review is shown.
@@ -7661,53 +7694,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="25">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="20" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B23" s="24" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="25"/>
     <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
@@ -8686,6 +8718,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -8719,7 +8754,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC13</t>
         </is>
@@ -8731,7 +8766,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), an Event Coordinator. Only an Organiser may raise an event request.</t>
         </is>
@@ -8743,7 +8778,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Type the New event request page address directly into the browser address bar and press Enter
 2. Wait for the page to finish loading</t>
@@ -8756,7 +8791,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator); Page requested: New event request</t>
         </is>
@@ -8768,7 +8803,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The page shows 'You do not have access to this' explaining that only an Event Organiser can raise an event request.
 The event request form — Event name, Type of event, Purpose, Starts at, Ends at — is not rendered at all, so there is nothing to fill in and no Save draft button to press.</t>
@@ -8781,7 +8816,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -8813,7 +8848,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>The page showed 'You do not have access to this - Only an Event Organiser can raise an event request. Coordinators and ConnectSphere staff work on requests once they have been submitted.' The form was not rendered at all: zero Event name fields and zero Save draft buttons on the page.</t>
         </is>
@@ -8837,7 +8872,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Previously this route rendered the whole form to any role and only refused on Save.</t>
         </is>
@@ -8849,7 +8884,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -8880,7 +8915,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The page shows 'You do not have access to this' explaining that only an Event Organiser can raise an event request.
 The event request form — Event name, Type of event, Purpose, Starts at, Ends at — is not rendered at all, so there is nothing to fill in and no Save draft button to press.</t>
@@ -8905,7 +8940,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -8917,7 +8952,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -9923,7 +9958,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -9931,235 +9966,241 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-22-TC14</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Logged in as Daniel Lim (daniel.lim@example.com / password123), an Attendee.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-22-TC14</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44.25" customHeight="1" s="25">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Logged in as Daniel Lim (daniel.lim@example.com / password123), an Attendee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="25">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Type the Assignments page address directly into the browser address bar and press Enter
 2. Wait for the page to finish loading</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Account: daniel.lim@example.com (Attendee); Page requested: Assignments</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="57.75" customHeight="1" s="25">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Account: daniel.lim@example.com (Attendee); Page requested: Assignments</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>The page shows 'You do not have access to this' explaining that assigning coordinators is the Event Operations Manager's role.
 No event awaiting assignment is listed.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="57.75" customHeight="1" s="25">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="57.75" customHeight="1" s="25">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>The page showed 'You do not have access to this - Assigning coordinators is the Event Operations Manager's role.' with a Back to Dashboard button. No event awaiting assignment was listed.</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" s="25">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>The page showed 'You do not have access to this - Assigning coordinators is the Event Operations Manager's role.' with a Back to Dashboard button. No event awaiting assignment was listed.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" s="25">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="25">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAN JORDAN </t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAN JORDAN </t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
-    <row r="17" ht="15.75" customHeight="1" s="25">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>The page shows 'You do not have access to this' explaining that assigning coordinators is the Event Operations Manager's role.
 No event awaiting assignment is listed.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="25">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B23" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="25"/>
     <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
@@ -11138,6 +11179,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -11171,7 +11215,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC15</t>
         </is>
@@ -11183,7 +11227,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>No one is signed in.</t>
         </is>
@@ -11195,7 +11239,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Type the Venues page address directly into the browser address bar and press Enter
 2. Wait for the page to finish loading
@@ -11209,7 +11253,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Page requested: Venues, with no session; Account used afterwards: marcus.wong@connectsphere.com</t>
         </is>
@@ -11221,7 +11265,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The browser lands on the Log in page showing 'Your session expired. Log in to continue where you left off.'
 No venue data is shown before logging in.
@@ -11235,7 +11279,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -11267,7 +11311,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Requesting Venues while signed out landed on /login?next=%2Fvenues showing 'Your session expired. Log in to continue where you left off.' No venue data appeared before logging in. After signing in as Venue Staff the browser opened the Venues page that had been asked for.</t>
         </is>
@@ -11291,7 +11335,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -11303,7 +11347,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -11334,7 +11378,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The browser lands on the Log in page showing 'Your session expired. Log in to continue where you left off.'
 No venue data is shown before logging in.
@@ -11360,7 +11404,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -11372,7 +11416,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12378,7 +12422,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -12386,45 +12430,52 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-22-TC16</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="44.25" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager, whose sidebar offers Assignments.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-22-TC16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44.25" customHeight="1" s="25">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager, whose sidebar offers Assignments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="25">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Click Assignments in the sidebar
 2. Wait for the page to finish loading
@@ -12432,25 +12483,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Account: grace.lim@connectsphere.com (Operations Manager)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="98.25" customHeight="1" s="25">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Account: grace.lim@connectsphere.com (Operations Manager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>The page is headed Assignments and explains that it will show submitted events waiting to be assigned to a coordinator.
 A notice reads 'This screen is not built yet', naming S-28 (Coordinator Assignment) and confirming the role does have access.
@@ -12458,113 +12509,113 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="71.25" customHeight="1" s="25">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="71.25" customHeight="1" s="25">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Clicking Assignments opened a page headed Assignments, describing submitted events waiting to be assigned, with the notice 'This screen is not built yet' naming S-28 (Coordinator Assignment) and confirming the role does have access. No 404 page appeared.</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" s="25">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Clicking Assignments opened a page headed Assignments, describing submitted events waiting to be assigned, with the notice 'This screen is not built yet' naming S-28 (Coordinator Assignment) and confirming the role does have access. No 404 page appeared.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" s="25">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="25">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAN JORDAN </t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAN JORDAN </t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
     <row r="17" ht="15.75" customHeight="1" s="25"/>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="25"/>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="B19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="25">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>The page is headed Assignments and explains that it will show submitted events waiting to be assigned to a coordinator.
 A notice reads 'This screen is not built yet', naming S-28 (Coordinator Assignment) and confirming the role does have access.
@@ -12572,53 +12623,52 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="25">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Screen should show the actual page later when the page has already been built leaving this expected results to be outdated</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Screen should show the actual page later when the page has already been built leaving this expected results to be outdated</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="25">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="25">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B24" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
     <row r="27" ht="15.75" customHeight="1" s="25"/>
@@ -13596,6 +13646,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -13629,7 +13682,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC17</t>
         </is>
@@ -13641,7 +13694,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Lim (daniel.lim@example.com / password123), an Attendee. A confirmed event that is open for registration exists and has a coordinator assigned, an expected attendance and special requirements recorded.</t>
         </is>
@@ -13653,7 +13706,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open the events list from the sidebar
 2. Open the first event in the list
@@ -13667,7 +13720,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.lim@example.com (Attendee)</t>
         </is>
@@ -13679,7 +13732,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The page shows the event's title, description, category, dates and status, and what is needed to register.
 There is no Coordinator row, no Organiser row, no Expected attendance row, no Special requirements row, no Rejection reason row and no venue or equipment arrangements.
@@ -13693,7 +13746,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -13725,7 +13778,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>On EVT-000013 as the Attendee the page showed Category, Status, When, Description, the client's COMPANY name, and the Registration capacity and window. Every row this case requires to be absent was absent: no Coordinator, no Organiser, no Expected attendance, no Special requirements, no Rejection reason, and no venue or equipment arrangements. The labels were not present-but-empty; they were not rendered at all.</t>
         </is>
@@ -13749,7 +13802,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>COMPANY (the client's name, not the organiser's) is shown to an Attendee by design - SPM-31 decided an attendee may see whose event they are registering for, and the rationale sits on ATTENDEE_EVENT_FIELDS in src/lib/permissions.ts. docs/PERMISSIONS.md section 4 had not been updated to record it, which is what made this look like a leak on the first run; section 4 now names both this exception and sequenceNumber. The organiser's personal name and the raw organisationId remain withheld, and a regression test in permissions.test.ts now pins both halves of that rule.</t>
         </is>
@@ -13761,7 +13814,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -13792,7 +13845,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The page shows EVT-000013 event's title, description, category, dates and status, and what is needed to register.
 There is no Coordinator row, no Organiser row, no Expected attendance row, no Special requirements row, no Rejection reason row and no venue or equipment arrangements.
@@ -13818,7 +13871,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Similar test case to TC-04</t>
         </is>
@@ -13830,7 +13883,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -14846,87 +14899,87 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="25">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="84.75" customHeight="1" s="25">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>AC2 says Venue Staff see Overview and Venue, but the Venue tab has no screen behind it yet (IMPLEMENTED_TABS in src/lib/eventTabs.ts limits the tab bar to Overview and Equipment). Venue Staff therefore see Overview alone today, which SPM-22-TC06 records. Is leaving an unbuilt-but-permitted tab out the behaviour you want, or should the tab appear and lead to a 'not built yet' screen the way the sidebar items now do?</t>
         </is>
       </c>
-      <c r="C2" s="15" t="n"/>
+      <c r="C2" s="29" t="n"/>
     </row>
     <row r="3" ht="111.75" customHeight="1" s="25">
-      <c r="A3" s="15" t="n">
+      <c r="A3" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-22 added seven placeholder screens (Review Queue, Assignments, Equipment, Equipment Requests, Booking Requests, Browse Events, My Registrations) plus Notifications, so that every sidebar item leads somewhere and AC4 can be tested on all of them. Each is permission-guarded first and empty second. Confirm this is the intended approach — the alternative was to hide sidebar items whose screens do not exist, which would have removed Assignments from the Operations Manager's sidebar and contradicted AC6.</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n"/>
+      <c r="C3" s="29" t="n"/>
     </row>
     <row r="4" ht="71.25" customHeight="1" s="25">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>AC3 was verified on the venue catalogue, which is the only screen today that renders the same route to two roles with different permissions. Once the review queue, booking and equipment screens are real, AC3 deserves a case on each of them; as written it can only be checked where a permitted and a refused role share a screen.</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n"/>
+      <c r="C4" s="29" t="n"/>
     </row>
     <row r="5" ht="71.25" customHeight="1" s="25">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>RESOLVED 2026-09-28. The migrations add_event_seed_key and add_event_sequence_number have been applied to the shared database, so the events list loads and every case in this workbook has now been executed. No reseed was needed: add_event_sequence_number adds its column with DEFAULT nextval(...), which backfilled the existing rows.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n"/>
+      <c r="C5" s="29" t="n"/>
     </row>
     <row r="6" ht="138.75" customHeight="1" s="25">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>RESOLVED 2026-09-28. SPM-22-TC17 first read as a leak: an Attendee is shown COMPANY, the client's name. It is deliberate - SPM-31 decided an attendee may see whose event they are registering for, and the rationale is written on ATTENDEE_EVENT_FIELDS in src/lib/permissions.ts. What was wrong was the documentation: docs/PERMISSIONS.md section 4 still listed eleven fields and said client identity was withheld. Section 4 now records both exceptions (organisation and sequenceNumber), and permissions.test.ts pins them, so the code and the document can no longer drift apart silently. The organiser's own name and the raw organisationId stay withheld.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n"/>
+      <c r="C6" s="29" t="n"/>
     </row>
     <row r="7" ht="138.75" customHeight="1" s="25">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Raised while executing SPM-22-TC05. Event tabs are filtered by role, but the Equipment tab's data is also gated by relationship: a coordinator who is not the assigned coordinator for an event still sees the Equipment tab, and opening it shows the generic 'Could not load equipment requirements.' error rather than an access-denied state (the request is refused with 403). AC3 and AC4 are written about role, so this is outside their letter, but the user-visible result is the 'shown then broken' pattern SPM-22 set out to remove. Should the tab bar take the relationship into account, or should the tab at least render the access-denied state instead of a load error?</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n"/>
+      <c r="C7" s="29" t="n"/>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="25"/>
     <row r="9" ht="12.75" customHeight="1" s="25"/>
@@ -15955,7 +16008,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC18</t>
         </is>
@@ -15967,7 +16020,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), an Event Coordinator, opening the same event used in SPM-22-TC17.</t>
         </is>
@@ -15979,7 +16032,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open All Events from the sidebar
 2. Open the same event used in SPM-22-TC17
@@ -15993,7 +16046,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator); the event opened in SPM-22-TC17</t>
         </is>
@@ -16005,7 +16058,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The Coordinator and Organiser rows are both shown with names, and Expected attendance is shown with its number.
 This confirms that the rows missing in SPM-22-TC17 are withheld from the Attendee rather than simply not recorded on that event.</t>
@@ -16018,7 +16071,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -16050,7 +16103,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>On the same event as the Coordinator, ORGANISER (Aaron Sim), COORDINATOR (Joel Fernandez) and EXPECTED ATTENDANCE (70) were all shown, along with Preferred layout, Required facilities, Accessibility notes and Special requirements.</t>
         </is>
@@ -16074,7 +16127,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Confirms the rows missing in SPM-22-TC17 are withheld from the Attendee rather than simply unrecorded on that event.</t>
         </is>
@@ -16086,7 +16139,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -16117,7 +16170,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The EVT-000013 event's Coordinator and Organiser rows are both shown with names, and Expected attendance is shown with its number.
 This confirms that the rows missing in SPM-22-TC17 are withheld from the Attendee rather than simply not recorded on that event.</t>
@@ -16142,7 +16195,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -16154,7 +16207,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17160,7 +17213,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -17168,70 +17221,77 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-22-TC19</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-22-TC19</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" s="25">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="25">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Read every item in the left sidebar from top to bottom
 2. Read the role shown beneath the name in the top bar</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Account: grace.lim@connectsphere.com (Operations Manager)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="98.25" customHeight="1" s="25">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Account: grace.lim@connectsphere.com (Operations Manager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>The sidebar reads exactly: Dashboard, Assignments, All Events, Notifications.
 The top bar shows Grace Lim with 'Operations Manager' beneath the name.
@@ -17239,112 +17299,112 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="57.75" customHeight="1" s="25">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="57.75" customHeight="1" s="25">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>The sidebar read exactly: Dashboard, Assignments, All Events, Notifications. The top bar showed Grace Lim with 'Operations Manager' beneath the name. Review Queue, Venues, Equipment and Booking Requests were absent.</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" s="25">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>The sidebar read exactly: Dashboard, Assignments, All Events, Notifications. The top bar showed Grace Lim with 'Operations Manager' beneath the name. Review Queue, Venues, Equipment and Booking Requests were absent.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" s="25">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="25">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAN JORDAN </t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAN JORDAN </t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
-    <row r="17" ht="15.75" customHeight="1" s="25">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>The sidebar reads exactly: Dashboard, Assignments, All Events, Notifications.
 The top bar shows Grace Lim with 'Operations Manager' beneath the name.
@@ -17352,53 +17412,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="25">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B23" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="25"/>
     <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
@@ -18377,6 +18436,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -18388,7 +18450,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="25" min="1" max="1"/>
@@ -18396,45 +18458,52 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-22-TC20</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-22-TC20</t>
         </is>
       </c>
     </row>
     <row r="4" ht="57.75" customHeight="1" s="25">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Logged in as Grace Lim (grace.lim@connectsphere.com / password123), an Operations Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="25">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Click Dashboard and wait for it to load
 2. Click Assignments and wait for it to load
@@ -18443,190 +18512,189 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Account: grace.lim@connectsphere.com (Operations Manager)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="57.75" customHeight="1" s="25">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Account: grace.lim@connectsphere.com (Operations Manager)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>All four screens open. None shows a 404 'page could not be found' error and none shows an access-denied message.
 Assignments and Notifications explain that they are not built yet; Dashboard and All Events show their real content.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="71.25" customHeight="1" s="25">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="71.25" customHeight="1" s="25">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>All four items opened: Dashboard (/dashboard) and All Events (/events) showed their real content; Assignments (/assignments) and Notifications (/notifications) showed their 'not built yet' notice. None of the four produced a 404 and none produced an access-denied state.</t>
-        </is>
-      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" s="25">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>All four items opened: Dashboard (/dashboard) and All Events (/events) showed their real content; Assignments (/assignments) and Notifications (/notifications) showed their 'not built yet' notice. None of the four produced a 404 and none produced an access-denied state.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1" s="25">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Before SPM-22 every one of these except Dashboard and All Events returned the Next.js 404 page.</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="25">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAN JORDAN </t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Before SPM-22 every one of these except Dashboard and All Events returned the Next.js 404 page.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAN JORDAN </t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
-    <row r="17" ht="15.75" customHeight="1" s="25">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>All four screens open. None shows a 404 'page could not be found' error and none shows an access-denied message.
 Assignments and Notifications explain that they are not built yet; Dashboard and All Events show their real content.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="25">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Before SPM-22 every one of these except Dashboard and All Events returned the Next.js 404 page.</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Before SPM-22 every one of these except Dashboard and All Events returned the Next.js 404 page.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B23" s="6" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="25"/>
     <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
@@ -19605,6 +19673,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -19638,7 +19709,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC01</t>
         </is>
@@ -19650,7 +19721,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Demo data is seeded. Logged in as Daniel Lim (daniel.lim@example.com / password123), an Attendee.</t>
         </is>
@@ -19662,7 +19733,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Read every item in the left sidebar from top to bottom</t>
         </is>
@@ -19674,7 +19745,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.lim@example.com (Attendee)</t>
         </is>
@@ -19686,7 +19757,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The sidebar reads exactly: Dashboard, Browse Events, My Registrations, Notifications.
 Review Queue, Venues, Equipment, Booking Requests and Assignments do not appear anywhere in the sidebar.</t>
@@ -19699,7 +19770,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -19731,7 +19802,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>The sidebar read exactly: Dashboard, Browse Events, My Registrations, Notifications. Review Queue, Venues, Equipment, Booking Requests and Assignments were absent.</t>
         </is>
@@ -19755,7 +19826,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -19767,7 +19838,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -19798,7 +19869,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The sidebar read exactly: Dashboard, Browse Events, My Registrations, Notifications. Review Queue, Venues, Equipment, Booking Requests and Assignments were absent.</t>
         </is>
@@ -19822,7 +19893,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -19834,7 +19905,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -20862,7 +20933,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC02</t>
         </is>
@@ -20874,7 +20945,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), an Event Coordinator.</t>
         </is>
@@ -20886,7 +20957,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Read every item in the left sidebar from top to bottom</t>
         </is>
@@ -20898,7 +20969,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator)</t>
         </is>
@@ -20910,7 +20981,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The sidebar reads exactly: Dashboard, Review Queue, All Events, Venues, Equipment, Notifications.
 Assignments, Booking Requests, Browse Events and My Registrations do not appear.</t>
@@ -20923,7 +20994,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -20955,7 +21026,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>The sidebar read exactly: Dashboard, Review Queue, All Events, Venues, Equipment, Notifications. Assignments, Booking Requests, Browse Events and My Registrations were absent.</t>
         </is>
@@ -20979,7 +21050,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -20991,7 +21062,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -21022,7 +21093,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The sidebar read exactly: Dashboard, Review Queue, All Events, Venues, Equipment, Notifications. Assignments, Booking Requests, Browse Events and My Registrations were absent.</t>
         </is>
@@ -21046,7 +21117,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -21058,7 +21129,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22086,7 +22157,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC03</t>
         </is>
@@ -22098,7 +22169,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Demo data is seeded. No one is signed in.</t>
         </is>
@@ -22110,7 +22181,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com with password123 and write down the sidebar
 2. Log out, then log in as kenji.sato@connectsphere.com with password123
@@ -22124,7 +22195,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Accounts: marcus.wong@connectsphere.com (Venue Staff), kenji.sato@connectsphere.com (Technical Support); Password: password123</t>
         </is>
@@ -22136,7 +22207,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Marcus Wong's sidebar reads: Dashboard, Venues, Booking Requests, Notifications.
 Kenji Sato's sidebar reads: Dashboard, Equipment, Equipment Requests, Notifications.
@@ -22150,7 +22221,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -22182,7 +22253,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Marcus Wong (Venue Staff): Dashboard, Venues, Booking Requests, Notifications. Kenji Sato (Technical Support): Dashboard, Equipment, Equipment Requests, Notifications. Neither sidebar carried the other's working screens, and the chrome was identical for both.</t>
         </is>
@@ -22206,7 +22277,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -22218,7 +22289,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -22249,7 +22320,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Marcus Wong (Venue Staff): Dashboard, Venues, Booking Requests, Notifications. Kenji Sato (Technical Support): Dashboard, Equipment, Equipment Requests, Notifications. Neither sidebar carried the other's working screens, and the chrome was identical for both.</t>
         </is>
@@ -22273,7 +22344,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -22285,7 +22356,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -23313,7 +23384,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC04</t>
         </is>
@@ -23325,7 +23396,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Lim (daniel.lim@example.com / password123), an Attendee. At least one confirmed event that is open for registration exists.</t>
         </is>
@@ -23337,7 +23408,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open the events list from the sidebar
 2. Open the first event in the list
@@ -23351,7 +23422,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.lim@example.com (Attendee)</t>
         </is>
@@ -23363,7 +23434,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Only an Overview tab is shown.
 No Equipment, Venue, Discussion, Attendees, Readiness or History tab appears — not even greyed out.</t>
@@ -23376,7 +23447,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -23408,7 +23479,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Opened EVT-000013 (Tanjong Legal CPD Seminar) as the Attendee. The tab bar contained one tab, Overview. No Equipment, Venue, Discussion, Attendees, Readiness or History tab was present, greyed out or otherwise.</t>
         </is>
@@ -23432,7 +23503,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -23444,7 +23515,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -23475,7 +23546,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Opened EVT-000013 (Tanjong Legal CPD Seminar) as the Attendee. The tab bar contained one tab, Overview. No Equipment, Venue, Discussion, Attendees, Readiness or History tab was present, greyed out or otherwise.</t>
         </is>
@@ -23499,7 +23570,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -23511,7 +23582,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -24539,7 +24610,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC05</t>
         </is>
@@ -24551,7 +24622,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), an Event Coordinator, with at least one event visible in All Events.</t>
         </is>
@@ -24563,7 +24634,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open All Events from the sidebar
 2. Open the first event in the list
@@ -24577,7 +24648,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator)</t>
         </is>
@@ -24589,7 +24660,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Both an Overview tab and an Equipment tab are shown, and clicking Equipment opens the equipment requirements for that event.
 Discussion, Venue, Attendees, Readiness and History are not shown, because those screens are not built yet — a tab that leads nowhere is left out rather than shown broken.</t>
@@ -24602,7 +24673,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -24634,7 +24705,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>As the Coordinator the tab bar showed Overview and Equipment. Clicking Equipment opened /events/EVT-000004/equipment, headed 'Equipment requirements', listing that event's recorded items. Discussion, Venue, Attendees, Readiness and History were not shown.</t>
         </is>
@@ -24658,7 +24729,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Run against EVT-000004, an event Daniel Tan is the assigned coordinator for. Worth knowing: on an event he is NOT assigned to (EVT-000023, coordinator Joel Fernandez) the Equipment tab is still offered, and opening it shows the generic 'Could not load equipment requirements.' error rather than an access-denied state - the request is refused with 403. Tabs are filtered by role; this refusal is by relationship, which the tab bar does not know about. See open question 5.</t>
         </is>
@@ -24670,7 +24741,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -24701,7 +24772,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>As the Coordinator the tab bar showed Overview and Equipment. Clicking Equipment opened /events/EVT-000110/equipment, headed 'Equipment requirements', listing that event's recorded items. Discussion, Venue, Attendees, Readiness and History were not shown.</t>
         </is>
@@ -24725,7 +24796,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -24737,7 +24808,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -25765,7 +25836,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC06</t>
         </is>
@@ -25777,7 +25848,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff, viewing an event Venue Staff is allowed to see.</t>
         </is>
@@ -25789,7 +25860,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open an event from the events list
 2. Read the row of tabs beneath the event title</t>
@@ -25802,7 +25873,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: marcus.wong@connectsphere.com (Venue Staff)</t>
         </is>
@@ -25814,7 +25885,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Only an Overview tab is shown.
 No Equipment tab appears, because Venue Staff are not permitted it.
@@ -25828,7 +25899,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -25860,7 +25931,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>As Venue Staff the tab bar contained one tab, Overview. No Equipment tab was offered.</t>
         </is>
@@ -25884,7 +25955,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Passes as the case is written. Note the deviation the case itself records: AC2 names Overview AND Venue for this role, but the Venue screen is not built, so eventTabs.ts leaves the tab out entirely. See open question 1.</t>
         </is>
@@ -25896,7 +25967,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -25927,7 +25998,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Only an Overview tab is shown.
 No Equipment tab appears, because Venue Staff are not permitted it.
@@ -25953,7 +26024,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -25965,7 +26036,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -26993,7 +27064,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-22-TC07</t>
         </is>
@@ -27005,7 +27076,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), an Event Coordinator, who may read the venue catalogue but not change it.</t>
         </is>
@@ -27017,7 +27088,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Open Venues from the sidebar
 2. Wait for the venue list to finish loading
@@ -27031,7 +27102,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: daniel.tan@connectsphere.com (Event Coordinator)</t>
         </is>
@@ -27043,7 +27114,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>The venue list is shown in full and is readable.
 There is no Add venue button at all — not a greyed-out one, and not one that shows a message when clicked.
@@ -27057,7 +27128,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -27089,7 +27160,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>The venue list rendered in full - 16 venue rows, readable. There was no Add venue button anywhere on the page. Clicking a venue row did not navigate: the address stayed on the Venues list.</t>
         </is>
@@ -27113,7 +27184,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -27125,7 +27196,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
@@ -27156,7 +27227,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>The venue list is shown in full and is readable.
 There is no Add venue button at all — not a greyed-out one, and not one that shows a message when clicked.
@@ -27182,7 +27253,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -27194,7 +27265,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
